--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
@@ -136,10 +136,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -171,10 +171,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1575,9 +1575,329 @@
         <v>6000</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>01/09/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C23" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E23" t="str">
+        <v>เงินเดือนพนักงาน ส.ค. (owner allocation from pooled transfers 25/26/27)</v>
+      </c>
+      <c r="F23">
+        <v>23200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>04/08/2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C24" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Ming manager wage Aug (1/3 of ฿20,000; slips 98+64)</v>
+      </c>
+      <c r="F24">
+        <v>6666.67</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>24/08/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C25" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E25" t="str">
+        <v>เครื่องสกัดเย็น 1,142 + เต็นท์ 1,923 (1/3 equal split)</v>
+      </c>
+      <c r="F25">
+        <v>1021.67</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>29/08/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C26" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E26" t="str">
+        <v>ค่าใช้จ่ายดำเนินงาน (ผู้จัดการซื้อ, ไม่มีบันทึกในสลิป) (1/3 equal split)</v>
+      </c>
+      <c r="F26">
+        <v>792.33</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>04/08/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C27" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Salary trainee: k 800, chang 1,200, mai 400 (1/3 equal split)</v>
+      </c>
+      <c r="F27">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>08/08/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C28" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Salary special event 1 person (1/3 equal split)</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>30/08/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C29" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E29" t="str">
+        <v>ค่าปริ้นเอกสาร (1/3 equal split)</v>
+      </c>
+      <c r="F29">
+        <v>63.33</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>21/08/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C30" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E30" t="str">
+        <v>ป้าย QR code ใหม่ 4 อัน (1/3 equal split)</v>
+      </c>
+      <c r="F30">
+        <v>48.33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>03/08/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C31" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E31" t="str">
+        <v>ค่าเช่า stock เดือน august (1/3 split)</v>
+      </c>
+      <c r="F31">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>01/08/2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C32" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E32" t="str">
+        <v>ค่าเช่าที่ B2 เดือน august (part 1 of 2)</v>
+      </c>
+      <c r="F32">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>01/08/2026</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C33" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E33" t="str">
+        <v>ค่าเช่าที่ B2 เดือน august (part 2 of 2)</v>
+      </c>
+      <c r="F33">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>03/08/2026</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C34" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E34" t="str">
+        <v>ค่ายกของ (1/3 equal split)</v>
+      </c>
+      <c r="F34">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>06/08/2026</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C35" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E35" t="str">
+        <v>กล้องวงจรปิด 1 ตัว</v>
+      </c>
+      <c r="F35">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>11/08/2026</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C36" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E36" t="str">
+        <v>โต๊ะ 1 ตัว</v>
+      </c>
+      <c r="F36">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>15/08/2026</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C37" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E37" t="str">
+        <v>อุปกรณ์ตกแต่งร้าน (50:50 B1/B2)</v>
+      </c>
+      <c r="F37">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>15/08/2026</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Aug26</v>
+      </c>
+      <c r="C38" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E38" t="str">
+        <v>โต๊ะ 594 + เขียง 208 (equal split B1/B2)</v>
+      </c>
+      <c r="F38">
+        <v>401</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F38"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7852,10 +8172,10 @@
         <v>Thu</v>
       </c>
       <c r="C19">
-        <v>1740</v>
+        <v>1770</v>
       </c>
       <c r="D19">
-        <v>1390</v>
+        <v>1420</v>
       </c>
       <c r="E19">
         <v>60</v>
@@ -12282,7 +12602,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12344,10 +12664,531 @@
       <c r="R3" t="str">
         <v>Used Watermelon (pcs)</v>
       </c>
+      <c r="S3" t="str">
+        <v>Source Note</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>01/08/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C4">
+        <v>6020</v>
+      </c>
+      <c r="D4">
+        <v>4290</v>
+      </c>
+      <c r="G4">
+        <v>1730</v>
+      </c>
+      <c r="S4" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>02/08/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C5">
+        <v>3460</v>
+      </c>
+      <c r="S5" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>03/08/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C6">
+        <v>4990</v>
+      </c>
+      <c r="S6" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>04/08/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C7">
+        <v>3660</v>
+      </c>
+      <c r="D7">
+        <v>3330</v>
+      </c>
+      <c r="G7">
+        <v>330</v>
+      </c>
+      <c r="S7" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>05/08/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C8">
+        <v>2900</v>
+      </c>
+      <c r="S8" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>06/08/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C9">
+        <v>4240</v>
+      </c>
+      <c r="S9" t="str">
+        <v>[ESTIMATED] ESTIMATED — same-weekday mean of 3 days. NOT observed. Replace when real data arrives.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>07/08/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C10">
+        <v>4670</v>
+      </c>
+      <c r="D10">
+        <v>3200</v>
+      </c>
+      <c r="G10">
+        <v>1470</v>
+      </c>
+      <c r="S10" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>08/08/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C11">
+        <v>4880</v>
+      </c>
+      <c r="S11" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>09/08/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C12">
+        <v>7810</v>
+      </c>
+      <c r="S12" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>10/08/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C13">
+        <v>5150</v>
+      </c>
+      <c r="S13" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>11/08/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C14">
+        <v>6010</v>
+      </c>
+      <c r="D14">
+        <v>4500</v>
+      </c>
+      <c r="G14">
+        <v>1510</v>
+      </c>
+      <c r="S14" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>12/08/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C15">
+        <v>4950</v>
+      </c>
+      <c r="S15" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>13/08/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C16">
+        <v>5110</v>
+      </c>
+      <c r="S16" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>14/08/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C17">
+        <v>5170</v>
+      </c>
+      <c r="S17" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>15/08/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C18">
+        <v>5550</v>
+      </c>
+      <c r="S18" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>16/08/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C19">
+        <v>5010</v>
+      </c>
+      <c r="D19">
+        <v>3540</v>
+      </c>
+      <c r="G19">
+        <v>1470</v>
+      </c>
+      <c r="S19" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>17/08/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C20">
+        <v>2500</v>
+      </c>
+      <c r="S20" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>18/08/2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C21">
+        <v>4190</v>
+      </c>
+      <c r="S21" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>19/08/2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C22">
+        <v>3640</v>
+      </c>
+      <c r="S22" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>20/08/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C23">
+        <v>3270</v>
+      </c>
+      <c r="S23" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>21/08/2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C24">
+        <v>4140</v>
+      </c>
+      <c r="S24" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>22/08/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C25">
+        <v>4810</v>
+      </c>
+      <c r="S25" t="str">
+        <v>cash/scan breakdown not available — left blank, not zero. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>23/08/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C26">
+        <v>4038</v>
+      </c>
+      <c r="D26">
+        <v>3218</v>
+      </c>
+      <c r="G26">
+        <v>820</v>
+      </c>
+      <c r="S26" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>24/08/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C27">
+        <v>4715</v>
+      </c>
+      <c r="D27">
+        <v>3290</v>
+      </c>
+      <c r="G27">
+        <v>1425</v>
+      </c>
+      <c r="S27" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>25/08/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C28">
+        <v>4825</v>
+      </c>
+      <c r="D28">
+        <v>3970</v>
+      </c>
+      <c r="G28">
+        <v>855</v>
+      </c>
+      <c r="S28" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>26/08/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C29">
+        <v>4100</v>
+      </c>
+      <c r="D29">
+        <v>3080</v>
+      </c>
+      <c r="G29">
+        <v>1020</v>
+      </c>
+      <c r="S29" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>27/08/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C30">
+        <v>4340</v>
+      </c>
+      <c r="D30">
+        <v>3600</v>
+      </c>
+      <c r="G30">
+        <v>740</v>
+      </c>
+      <c r="S30" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>28/08/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C31">
+        <v>2170</v>
+      </c>
+      <c r="D31">
+        <v>1020</v>
+      </c>
+      <c r="G31">
+        <v>1090</v>
+      </c>
+      <c r="S31" t="str">
+        <v>CHANNEL SPLIT DOES NOT SUM: cash 1020 + scan 1090 = 2110 vs recorded total 2170 (diff 60). Recorded as written; NOT balanced. OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>29/08/2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C32">
+        <v>3125</v>
+      </c>
+      <c r="D32">
+        <v>1850</v>
+      </c>
+      <c r="G32">
+        <v>1275</v>
+      </c>
+      <c r="S32" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>30/08/2026</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C33">
+        <v>4265</v>
+      </c>
+      <c r="D33">
+        <v>3610</v>
+      </c>
+      <c r="G33">
+        <v>655</v>
+      </c>
+      <c r="S33" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>31/08/2026</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C34">
+        <v>1505</v>
+      </c>
+      <c r="D34">
+        <v>1000</v>
+      </c>
+      <c r="G34">
+        <v>505</v>
+      </c>
+      <c r="S34" t="str">
+        <v>OCR JSON b2_august_1 (original photos expired on LINE and were deleted — no source image exists)</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S34"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
@@ -136,10 +136,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -171,10 +171,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -9749,19 +9749,19 @@
         <v>Wed</v>
       </c>
       <c r="C3">
-        <v>5200</v>
+        <v>2310</v>
       </c>
       <c r="D3">
-        <v>3010</v>
+        <v>1470</v>
       </c>
       <c r="E3">
         <v>60</v>
       </c>
       <c r="F3">
-        <v>2950</v>
+        <v>1410</v>
       </c>
       <c r="G3">
-        <v>2190</v>
+        <v>840</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -9791,7 +9791,7 @@
         <v>7</v>
       </c>
       <c r="Q3">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -10028,7 +10028,7 @@
         <v>5200</v>
       </c>
       <c r="D6">
-        <v>3000</v>
+        <v>3010</v>
       </c>
       <c r="E6">
         <v>60</v>
@@ -10037,7 +10037,7 @@
         <v>2940</v>
       </c>
       <c r="G6">
-        <v>2200</v>
+        <v>2190</v>
       </c>
       <c r="H6">
         <v>10</v>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
@@ -136,10 +136,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -171,10 +171,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -756,11 +756,11 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:AF29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Som Sai Jai Cold Press Bar - September 2026</v>
+        <v>Som Sai Jai Cold Press Bar (B2) - September 2026</v>
       </c>
     </row>
     <row r="3">
@@ -789,39 +789,2629 @@
         <v>Orange</v>
       </c>
       <c r="I3" t="str">
+        <v>Orange (100)</v>
+      </c>
+      <c r="J3" t="str">
         <v>Watermelon</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>Mango</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>Coconut</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>Apple</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>Young Coco</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="Q3" t="str">
         <v>Total Cups</v>
       </c>
-      <c r="O3" t="str">
+      <c r="R3" t="str">
         <v>Bot Big</v>
       </c>
-      <c r="P3" t="str">
+      <c r="S3" t="str">
         <v>Bot Small</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="T3" t="str">
         <v>Used Orange (basket)</v>
       </c>
-      <c r="R3" t="str">
+      <c r="U3" t="str">
         <v>Used Watermelon (pcs)</v>
+      </c>
+      <c r="V3" t="str">
+        <v>Used Mango</v>
+      </c>
+      <c r="W3" t="str">
+        <v>Used Coco (Meat)</v>
+      </c>
+      <c r="X3" t="str">
+        <v>Used Coco (Water)</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Used Coco (Conden)</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>Used Coco (Raw)</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>Used Apple</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>Used Guava</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>Used Pineapple</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>Used Young Coco</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>Bottle Revenue (฿)</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>Source Note</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>01/09/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C4">
+        <v>1900</v>
+      </c>
+      <c r="D4">
+        <v>1255</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+      <c r="F4">
+        <v>1840</v>
+      </c>
+      <c r="G4">
+        <v>645</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>13</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>29</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>13</v>
+      </c>
+      <c r="V4">
+        <v>2</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>10</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>SRC-B2-SEP-01</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>02/09/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C5">
+        <v>2815</v>
+      </c>
+      <c r="D5">
+        <v>1355</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+      <c r="F5">
+        <v>2755</v>
+      </c>
+      <c r="G5">
+        <v>1460</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>16</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>10</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
+        <v>42</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <v>16</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>5</v>
+      </c>
+      <c r="AA5">
+        <v>2</v>
+      </c>
+      <c r="AB5">
+        <v>10</v>
+      </c>
+      <c r="AC5">
+        <v>3</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>SRC-B2-SEP-02</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>03/09/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C6">
+        <v>1325</v>
+      </c>
+      <c r="D6">
+        <v>940</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>1265</v>
+      </c>
+      <c r="G6">
+        <v>385</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>20</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>9</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>3</v>
+      </c>
+      <c r="AA6">
+        <v>3</v>
+      </c>
+      <c r="AB6">
+        <v>2</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>SRC-B2-SEP-03</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>04/09/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C7">
+        <v>4005</v>
+      </c>
+      <c r="D7">
+        <v>2500</v>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+      <c r="F7">
+        <v>3945</v>
+      </c>
+      <c r="G7">
+        <v>1505</v>
+      </c>
+      <c r="H7">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>17</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>9</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+      <c r="Q7">
+        <v>50</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>11</v>
+      </c>
+      <c r="U7">
+        <v>17</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>4</v>
+      </c>
+      <c r="AA7">
+        <v>5</v>
+      </c>
+      <c r="AB7">
+        <v>9</v>
+      </c>
+      <c r="AC7">
+        <v>3</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>SRC-B2-SEP-04</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>05/09/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C8">
+        <v>1915</v>
+      </c>
+      <c r="D8">
+        <v>1340</v>
+      </c>
+      <c r="E8">
+        <v>60</v>
+      </c>
+      <c r="F8">
+        <v>1855</v>
+      </c>
+      <c r="G8">
+        <v>545</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>11</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>28</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>2</v>
+      </c>
+      <c r="U8">
+        <v>11</v>
+      </c>
+      <c r="V8">
+        <v>2</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>5</v>
+      </c>
+      <c r="AA8">
+        <v>2</v>
+      </c>
+      <c r="AB8">
+        <v>5</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>SRC-B2-SEP-05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>06/09/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C9">
+        <v>824</v>
+      </c>
+      <c r="D9">
+        <v>660</v>
+      </c>
+      <c r="E9">
+        <v>60</v>
+      </c>
+      <c r="F9">
+        <v>764</v>
+      </c>
+      <c r="G9">
+        <v>164</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>13</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>8</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>2</v>
+      </c>
+      <c r="AA9">
+        <v>2</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>SRC-B2-SEP-06</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>07/09/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C10">
+        <v>4980</v>
+      </c>
+      <c r="D10">
+        <v>4125</v>
+      </c>
+      <c r="E10">
+        <v>60</v>
+      </c>
+      <c r="F10">
+        <v>4920</v>
+      </c>
+      <c r="G10">
+        <v>855</v>
+      </c>
+      <c r="H10">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>21</v>
+      </c>
+      <c r="K10">
+        <v>6</v>
+      </c>
+      <c r="L10">
+        <v>16</v>
+      </c>
+      <c r="M10">
+        <v>3</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>2</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>69</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>14</v>
+      </c>
+      <c r="U10">
+        <v>21</v>
+      </c>
+      <c r="V10">
+        <v>6</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>16</v>
+      </c>
+      <c r="AA10">
+        <v>3</v>
+      </c>
+      <c r="AB10">
+        <v>2</v>
+      </c>
+      <c r="AC10">
+        <v>3</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>SRC-B2-SEP-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>08/09/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C11">
+        <v>1645</v>
+      </c>
+      <c r="D11">
+        <v>890</v>
+      </c>
+      <c r="E11">
+        <v>60</v>
+      </c>
+      <c r="F11">
+        <v>1585</v>
+      </c>
+      <c r="G11">
+        <v>755</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>4</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>25</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>2</v>
+      </c>
+      <c r="U11">
+        <v>10</v>
+      </c>
+      <c r="V11">
+        <v>2</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>5</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>4</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>SRC-B2-SEP-08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>09/09/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C12">
+        <v>2535</v>
+      </c>
+      <c r="D12">
+        <v>1685</v>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="F12">
+        <v>2475</v>
+      </c>
+      <c r="G12">
+        <v>850</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>14</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12">
+        <v>4</v>
+      </c>
+      <c r="M12">
+        <v>4</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>4</v>
+      </c>
+      <c r="P12">
+        <v>4</v>
+      </c>
+      <c r="Q12">
+        <v>37</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>4</v>
+      </c>
+      <c r="U12">
+        <v>14</v>
+      </c>
+      <c r="V12">
+        <v>3</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>4</v>
+      </c>
+      <c r="AA12">
+        <v>4</v>
+      </c>
+      <c r="AB12">
+        <v>4</v>
+      </c>
+      <c r="AC12">
+        <v>4</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="str">
+        <v>SRC-B2-SEP-09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>10/09/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C13">
+        <v>1989</v>
+      </c>
+      <c r="D13">
+        <v>964</v>
+      </c>
+      <c r="E13">
+        <v>60</v>
+      </c>
+      <c r="F13">
+        <v>1929</v>
+      </c>
+      <c r="G13">
+        <v>1025</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>28</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>10</v>
+      </c>
+      <c r="U13">
+        <v>12</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>3</v>
+      </c>
+      <c r="AA13">
+        <v>2</v>
+      </c>
+      <c r="AB13">
+        <v>1</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="str">
+        <v>SRC-B2-SEP-10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>11/09/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C14">
+        <v>715</v>
+      </c>
+      <c r="D14">
+        <v>715</v>
+      </c>
+      <c r="E14">
+        <v>60</v>
+      </c>
+      <c r="F14">
+        <v>655</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>9</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>2</v>
+      </c>
+      <c r="U14">
+        <v>5</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>2</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="str">
+        <v>SRC-B2-SEP-11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>12/09/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C15">
+        <v>2100</v>
+      </c>
+      <c r="D15">
+        <v>1115</v>
+      </c>
+      <c r="E15">
+        <v>60</v>
+      </c>
+      <c r="F15">
+        <v>2040</v>
+      </c>
+      <c r="G15">
+        <v>985</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>6</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>3</v>
+      </c>
+      <c r="P15">
+        <v>4</v>
+      </c>
+      <c r="Q15">
+        <v>30</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>4</v>
+      </c>
+      <c r="U15">
+        <v>9</v>
+      </c>
+      <c r="V15">
+        <v>2</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>6</v>
+      </c>
+      <c r="AA15">
+        <v>2</v>
+      </c>
+      <c r="AB15">
+        <v>3</v>
+      </c>
+      <c r="AC15">
+        <v>4</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="str">
+        <v>SRC-B2-SEP-12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>13/09/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C16">
+        <v>2379</v>
+      </c>
+      <c r="D16">
+        <v>1465</v>
+      </c>
+      <c r="E16">
+        <v>60</v>
+      </c>
+      <c r="F16">
+        <v>2319</v>
+      </c>
+      <c r="G16">
+        <v>914</v>
+      </c>
+      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>6</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>4</v>
+      </c>
+      <c r="M16">
+        <v>8</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>5</v>
+      </c>
+      <c r="P16">
+        <v>4</v>
+      </c>
+      <c r="Q16">
+        <v>34</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>6</v>
+      </c>
+      <c r="U16">
+        <v>6</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>4</v>
+      </c>
+      <c r="AA16">
+        <v>8</v>
+      </c>
+      <c r="AB16">
+        <v>5</v>
+      </c>
+      <c r="AC16">
+        <v>4</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="str">
+        <v>SRC-B2-SEP-13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>14/09/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C17">
+        <v>1695</v>
+      </c>
+      <c r="D17">
+        <v>1160</v>
+      </c>
+      <c r="E17">
+        <v>60</v>
+      </c>
+      <c r="F17">
+        <v>1635</v>
+      </c>
+      <c r="G17">
+        <v>535</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>9</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>5</v>
+      </c>
+      <c r="M17">
+        <v>6</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>3</v>
+      </c>
+      <c r="P17">
+        <v>3</v>
+      </c>
+      <c r="Q17">
+        <v>27</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>9</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>5</v>
+      </c>
+      <c r="AA17">
+        <v>6</v>
+      </c>
+      <c r="AB17">
+        <v>3</v>
+      </c>
+      <c r="AC17">
+        <v>3</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>SRC-B2-SEP-14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>15/09/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C18">
+        <v>355</v>
+      </c>
+      <c r="D18">
+        <v>205</v>
+      </c>
+      <c r="E18">
+        <v>60</v>
+      </c>
+      <c r="F18">
+        <v>295</v>
+      </c>
+      <c r="G18">
+        <v>150</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>5</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>SRC-B2-SEP-15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>16/09/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C19">
+        <v>585</v>
+      </c>
+      <c r="D19">
+        <v>275</v>
+      </c>
+      <c r="E19">
+        <v>60</v>
+      </c>
+      <c r="F19">
+        <v>525</v>
+      </c>
+      <c r="G19">
+        <v>310</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>7</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>2</v>
+      </c>
+      <c r="U19">
+        <v>3</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>1</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="str">
+        <v>SRC-B2-SEP-16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>17/09/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C20">
+        <v>1479</v>
+      </c>
+      <c r="D20">
+        <v>1134</v>
+      </c>
+      <c r="E20">
+        <v>60</v>
+      </c>
+      <c r="F20">
+        <v>1419</v>
+      </c>
+      <c r="G20">
+        <v>345</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>12</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>5</v>
+      </c>
+      <c r="M20">
+        <v>3</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>24</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>2</v>
+      </c>
+      <c r="U20">
+        <v>12</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>5</v>
+      </c>
+      <c r="AA20">
+        <v>3</v>
+      </c>
+      <c r="AB20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>SRC-B2-SEP-17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>18/09/2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C21">
+        <v>2639</v>
+      </c>
+      <c r="D21">
+        <v>2000</v>
+      </c>
+      <c r="E21">
+        <v>60</v>
+      </c>
+      <c r="F21">
+        <v>2579</v>
+      </c>
+      <c r="G21">
+        <v>639</v>
+      </c>
+      <c r="H21">
+        <v>7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>16</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21">
+        <v>9</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>39</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>7</v>
+      </c>
+      <c r="U21">
+        <v>16</v>
+      </c>
+      <c r="V21">
+        <v>3</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>9</v>
+      </c>
+      <c r="AA21">
+        <v>2</v>
+      </c>
+      <c r="AB21">
+        <v>2</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="str">
+        <v>SRC-B2-SEP-18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>19/09/2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C22">
+        <v>1010</v>
+      </c>
+      <c r="D22">
+        <v>765</v>
+      </c>
+      <c r="E22">
+        <v>60</v>
+      </c>
+      <c r="F22">
+        <v>950</v>
+      </c>
+      <c r="G22">
+        <v>245</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>11</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>17</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>3</v>
+      </c>
+      <c r="U22">
+        <v>11</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+      <c r="AB22">
+        <v>1</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="str">
+        <v>SRC-B2-SEP-19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>23/09/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C23">
+        <v>1440</v>
+      </c>
+      <c r="D23">
+        <v>1085</v>
+      </c>
+      <c r="E23">
+        <v>60</v>
+      </c>
+      <c r="F23">
+        <v>1440</v>
+      </c>
+      <c r="G23">
+        <v>355</v>
+      </c>
+      <c r="H23">
+        <v>5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>13</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>3</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>23</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>5</v>
+      </c>
+      <c r="U23">
+        <v>13</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>3</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="str">
+        <v>SRC-B2-SEP-20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>24/09/2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C24">
+        <v>1240</v>
+      </c>
+      <c r="D24">
+        <v>590</v>
+      </c>
+      <c r="E24">
+        <v>60</v>
+      </c>
+      <c r="F24">
+        <v>1240</v>
+      </c>
+      <c r="G24">
+        <v>650</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="L24">
+        <v>5</v>
+      </c>
+      <c r="M24">
+        <v>6</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>19</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>4</v>
+      </c>
+      <c r="V24">
+        <v>3</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>5</v>
+      </c>
+      <c r="AA24">
+        <v>6</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="str">
+        <v>SRC-B2-SEP-21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>25/09/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C25">
+        <v>355</v>
+      </c>
+      <c r="D25">
+        <v>150</v>
+      </c>
+      <c r="E25">
+        <v>30</v>
+      </c>
+      <c r="F25">
+        <v>325</v>
+      </c>
+      <c r="G25">
+        <v>175</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>6</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>2</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>2</v>
+      </c>
+      <c r="AB25">
+        <v>1</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="str">
+        <v>SRC-B2-SEP-22</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>27/09/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C26">
+        <v>1190</v>
+      </c>
+      <c r="D26">
+        <v>705</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>1190</v>
+      </c>
+      <c r="G26">
+        <v>485</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>11</v>
+      </c>
+      <c r="K26">
+        <v>3</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26">
+        <v>2</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>21</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>2</v>
+      </c>
+      <c r="U26">
+        <v>11</v>
+      </c>
+      <c r="V26">
+        <v>3</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>3</v>
+      </c>
+      <c r="AA26">
+        <v>2</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="str">
+        <v>SRC-B2-SEP-23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>28/09/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C27">
+        <v>2885</v>
+      </c>
+      <c r="D27">
+        <v>2040</v>
+      </c>
+      <c r="E27">
+        <v>60</v>
+      </c>
+      <c r="F27">
+        <v>2885</v>
+      </c>
+      <c r="G27">
+        <v>845</v>
+      </c>
+      <c r="H27">
+        <v>8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>18</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>7</v>
+      </c>
+      <c r="M27">
+        <v>8</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>5</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>47</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>8</v>
+      </c>
+      <c r="U27">
+        <v>18</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>7</v>
+      </c>
+      <c r="AA27">
+        <v>8</v>
+      </c>
+      <c r="AB27">
+        <v>5</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="str">
+        <v>SRC-B2-SEP-24</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>29/09/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C28">
+        <v>2330</v>
+      </c>
+      <c r="D28">
+        <v>1170</v>
+      </c>
+      <c r="E28">
+        <v>60</v>
+      </c>
+      <c r="F28">
+        <v>2330</v>
+      </c>
+      <c r="G28">
+        <v>1220</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>12</v>
+      </c>
+      <c r="K28">
+        <v>3</v>
+      </c>
+      <c r="L28">
+        <v>14</v>
+      </c>
+      <c r="M28">
+        <v>5</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>38</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>4</v>
+      </c>
+      <c r="U28">
+        <v>12</v>
+      </c>
+      <c r="V28">
+        <v>3</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>14</v>
+      </c>
+      <c r="AA28">
+        <v>5</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="str">
+        <v>SRC-B2-SEP-25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C29">
+        <v>2530</v>
+      </c>
+      <c r="D29">
+        <v>1245</v>
+      </c>
+      <c r="E29">
+        <v>60</v>
+      </c>
+      <c r="F29">
+        <v>2530</v>
+      </c>
+      <c r="G29">
+        <v>1285</v>
+      </c>
+      <c r="H29">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>23</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>4</v>
+      </c>
+      <c r="M29">
+        <v>3</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>3</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>39</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>5</v>
+      </c>
+      <c r="U29">
+        <v>23</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>4</v>
+      </c>
+      <c r="AA29">
+        <v>3</v>
+      </c>
+      <c r="AB29">
+        <v>3</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="str">
+        <v>SRC-B2-SEP-26</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF29"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1168,7 +3758,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1895,9 +4485,109 @@
         <v>401</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>01/09/2026</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C39" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E39" t="str">
+        <v>ค่าเช่า B2 เดือนกันยายน (Slip 64)</v>
+      </c>
+      <c r="F39">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C40" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E40" t="str">
+        <v>ค่าเช่า storage เดือน 9 (1/4 split B2)</v>
+      </c>
+      <c r="F40">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C41" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E41" t="str">
+        <v>เงินเดือนพนักงาน B2 ก.ย. (Hpai 11,200 + Myat 11,600)</v>
+      </c>
+      <c r="F41">
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>04/09/2026</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C42" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Ming manager wage Sep (1/4 of ฿20,000; Slip 47)</v>
+      </c>
+      <c r="F42">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>30/09/2026</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Sep26</v>
+      </c>
+      <c r="C43" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Other OPEX</v>
+      </c>
+      <c r="E43" t="str">
+        <v>ค่าขนส่ง / logistics / supplies Sep (B2 portion 13.65%)</v>
+      </c>
+      <c r="F43">
+        <v>1692.79</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F43"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
@@ -756,7 +756,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF29"/>
+  <dimension ref="A1:AF32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2725,25 +2725,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>23/09/2026</v>
+        <v>20/09/2026</v>
       </c>
       <c r="B23" t="str">
-        <v>Wed</v>
+        <v>Sun</v>
       </c>
       <c r="C23">
-        <v>1440</v>
+        <v>3270</v>
       </c>
       <c r="D23">
-        <v>1085</v>
+        <v>2480</v>
       </c>
       <c r="E23">
         <v>60</v>
       </c>
       <c r="F23">
-        <v>1440</v>
+        <v>3210</v>
       </c>
       <c r="G23">
-        <v>355</v>
+        <v>790</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -2752,28 +2752,28 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>3</v>
       </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -2785,10 +2785,10 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -2800,16 +2800,16 @@
         <v>0</v>
       </c>
       <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
         <v>3</v>
       </c>
-      <c r="AA23">
-        <v>1</v>
-      </c>
       <c r="AB23">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -2818,91 +2818,91 @@
         <v>0</v>
       </c>
       <c r="AF23" t="str">
-        <v>SRC-B2-SEP-20</v>
+        <v>SRC-B2-SEP-27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>24/09/2026</v>
+        <v>21/09/2026</v>
       </c>
       <c r="B24" t="str">
-        <v>Thu</v>
+        <v>Mon</v>
       </c>
       <c r="C24">
-        <v>1240</v>
+        <v>875</v>
       </c>
       <c r="D24">
-        <v>590</v>
+        <v>710</v>
       </c>
       <c r="E24">
         <v>60</v>
       </c>
       <c r="F24">
-        <v>1240</v>
+        <v>815</v>
       </c>
       <c r="G24">
-        <v>650</v>
+        <v>165</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
+        <v>5</v>
+      </c>
+      <c r="K24">
+        <v>2</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>4</v>
       </c>
-      <c r="K24">
-        <v>3</v>
-      </c>
-      <c r="L24">
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>13</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>2</v>
+      </c>
+      <c r="U24">
         <v>5</v>
       </c>
-      <c r="M24">
-        <v>6</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>19</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24">
+      <c r="V24">
+        <v>2</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
         <v>4</v>
       </c>
-      <c r="V24">
-        <v>3</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>5</v>
-      </c>
-      <c r="AA24">
-        <v>6</v>
-      </c>
       <c r="AB24">
         <v>0</v>
       </c>
@@ -2916,75 +2916,75 @@
         <v>0</v>
       </c>
       <c r="AF24" t="str">
-        <v>SRC-B2-SEP-21</v>
+        <v>SRC-B2-SEP-28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>25/09/2026</v>
+        <v>22/09/2026</v>
       </c>
       <c r="B25" t="str">
-        <v>Fri</v>
+        <v>Tue</v>
       </c>
       <c r="C25">
-        <v>355</v>
+        <v>2365</v>
       </c>
       <c r="D25">
-        <v>150</v>
+        <v>1745</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F25">
-        <v>325</v>
+        <v>2305</v>
       </c>
       <c r="G25">
-        <v>175</v>
+        <v>620</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25">
+        <v>33</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
         <v>6</v>
       </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
       <c r="U25">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -2996,13 +2996,13 @@
         <v>0</v>
       </c>
       <c r="Z25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -3014,60 +3014,60 @@
         <v>0</v>
       </c>
       <c r="AF25" t="str">
-        <v>SRC-B2-SEP-22</v>
+        <v>SRC-B2-SEP-29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>27/09/2026</v>
+        <v>23/09/2026</v>
       </c>
       <c r="B26" t="str">
-        <v>Sun</v>
+        <v>Wed</v>
       </c>
       <c r="C26">
-        <v>1190</v>
+        <v>1440</v>
       </c>
       <c r="D26">
-        <v>705</v>
+        <v>1085</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F26">
-        <v>1190</v>
+        <v>1440</v>
       </c>
       <c r="G26">
-        <v>485</v>
+        <v>355</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <v>3</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -3076,13 +3076,13 @@
         <v>0</v>
       </c>
       <c r="T26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -3097,10 +3097,10 @@
         <v>3</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -3112,93 +3112,93 @@
         <v>0</v>
       </c>
       <c r="AF26" t="str">
-        <v>SRC-B2-SEP-23</v>
+        <v>SRC-B2-SEP-20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>28/09/2026</v>
+        <v>24/09/2026</v>
       </c>
       <c r="B27" t="str">
-        <v>Mon</v>
+        <v>Thu</v>
       </c>
       <c r="C27">
-        <v>2885</v>
+        <v>1240</v>
       </c>
       <c r="D27">
-        <v>2040</v>
+        <v>590</v>
       </c>
       <c r="E27">
         <v>60</v>
       </c>
       <c r="F27">
-        <v>2885</v>
+        <v>1240</v>
       </c>
       <c r="G27">
-        <v>845</v>
+        <v>650</v>
       </c>
       <c r="H27">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>0</v>
       </c>
       <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>19</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>4</v>
+      </c>
+      <c r="V27">
+        <v>3</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
         <v>5</v>
       </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>47</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>8</v>
-      </c>
-      <c r="U27">
-        <v>18</v>
-      </c>
-      <c r="V27">
-        <v>1</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>7</v>
-      </c>
       <c r="AA27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -3210,60 +3210,60 @@
         <v>0</v>
       </c>
       <c r="AF27" t="str">
-        <v>SRC-B2-SEP-24</v>
+        <v>SRC-B2-SEP-21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>29/09/2026</v>
+        <v>25/09/2026</v>
       </c>
       <c r="B28" t="str">
-        <v>Tue</v>
+        <v>Fri</v>
       </c>
       <c r="C28">
-        <v>2330</v>
+        <v>355</v>
       </c>
       <c r="D28">
-        <v>1170</v>
+        <v>150</v>
       </c>
       <c r="E28">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F28">
-        <v>2330</v>
+        <v>325</v>
       </c>
       <c r="G28">
-        <v>1220</v>
+        <v>175</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N28">
         <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3272,13 +3272,13 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W28">
         <v>0</v>
@@ -3290,13 +3290,13 @@
         <v>0</v>
       </c>
       <c r="Z28">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -3308,110 +3308,404 @@
         <v>0</v>
       </c>
       <c r="AF28" t="str">
-        <v>SRC-B2-SEP-25</v>
+        <v>SRC-B2-SEP-22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
+        <v>27/09/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C29">
+        <v>1190</v>
+      </c>
+      <c r="D29">
+        <v>705</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1190</v>
+      </c>
+      <c r="G29">
+        <v>485</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>11</v>
+      </c>
+      <c r="K29">
+        <v>3</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>21</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>2</v>
+      </c>
+      <c r="U29">
+        <v>11</v>
+      </c>
+      <c r="V29">
+        <v>3</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>3</v>
+      </c>
+      <c r="AA29">
+        <v>2</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="str">
+        <v>SRC-B2-SEP-23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>28/09/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C30">
+        <v>2885</v>
+      </c>
+      <c r="D30">
+        <v>2040</v>
+      </c>
+      <c r="E30">
+        <v>60</v>
+      </c>
+      <c r="F30">
+        <v>2885</v>
+      </c>
+      <c r="G30">
+        <v>845</v>
+      </c>
+      <c r="H30">
+        <v>8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>18</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>7</v>
+      </c>
+      <c r="M30">
+        <v>8</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>5</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>47</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>8</v>
+      </c>
+      <c r="U30">
+        <v>18</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>7</v>
+      </c>
+      <c r="AA30">
+        <v>8</v>
+      </c>
+      <c r="AB30">
+        <v>5</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="str">
+        <v>SRC-B2-SEP-24</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>29/09/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C31">
+        <v>2330</v>
+      </c>
+      <c r="D31">
+        <v>1170</v>
+      </c>
+      <c r="E31">
+        <v>60</v>
+      </c>
+      <c r="F31">
+        <v>2330</v>
+      </c>
+      <c r="G31">
+        <v>1220</v>
+      </c>
+      <c r="H31">
+        <v>4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <v>3</v>
+      </c>
+      <c r="L31">
+        <v>14</v>
+      </c>
+      <c r="M31">
+        <v>5</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>38</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>4</v>
+      </c>
+      <c r="U31">
+        <v>12</v>
+      </c>
+      <c r="V31">
+        <v>3</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>14</v>
+      </c>
+      <c r="AA31">
+        <v>5</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="str">
+        <v>SRC-B2-SEP-25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
         <v>30/09/2026</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B32" t="str">
         <v>Wed</v>
       </c>
-      <c r="C29">
+      <c r="C32">
         <v>2530</v>
       </c>
-      <c r="D29">
+      <c r="D32">
         <v>1245</v>
       </c>
-      <c r="E29">
+      <c r="E32">
         <v>60</v>
       </c>
-      <c r="F29">
+      <c r="F32">
         <v>2530</v>
       </c>
-      <c r="G29">
+      <c r="G32">
         <v>1285</v>
       </c>
-      <c r="H29">
+      <c r="H32">
         <v>5</v>
       </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
         <v>23</v>
       </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29">
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
         <v>4</v>
       </c>
-      <c r="M29">
+      <c r="M32">
         <v>3</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
         <v>3</v>
       </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
         <v>39</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
         <v>5</v>
       </c>
-      <c r="U29">
+      <c r="U32">
         <v>23</v>
       </c>
-      <c r="V29">
-        <v>1</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
+      <c r="V32">
+        <v>1</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
         <v>4</v>
       </c>
-      <c r="AA29">
+      <c r="AA32">
         <v>3</v>
       </c>
-      <c r="AB29">
+      <c r="AB32">
         <v>3</v>
       </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="str">
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="str">
         <v>SRC-B2-SEP-26</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AF29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4579,10 +4873,10 @@
         <v>Other OPEX</v>
       </c>
       <c r="E43" t="str">
-        <v>ค่าขนส่ง / logistics / supplies Sep (B2 portion 13.65%)</v>
+        <v>ค่าขนส่ง / logistics / supplies Sep (B2 portion 15.19%)</v>
       </c>
       <c r="F43">
-        <v>1692.79</v>
+        <v>1883.74</v>
       </c>
     </row>
   </sheetData>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B2_2026.xlsx
@@ -136,10 +136,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -171,10 +171,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -3712,7 +3712,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:AF20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3745,39 +3745,883 @@
         <v>Orange</v>
       </c>
       <c r="I3" t="str">
+        <v>Orange (100)</v>
+      </c>
+      <c r="J3" t="str">
         <v>Watermelon</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>Mango</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>Coconut</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>Apple</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>Young Coco</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="Q3" t="str">
         <v>Total Cups</v>
       </c>
-      <c r="O3" t="str">
+      <c r="R3" t="str">
         <v>Bot Big</v>
       </c>
-      <c r="P3" t="str">
+      <c r="S3" t="str">
         <v>Bot Small</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="T3" t="str">
         <v>Used Orange (basket)</v>
       </c>
-      <c r="R3" t="str">
+      <c r="U3" t="str">
         <v>Used Watermelon (pcs)</v>
+      </c>
+      <c r="V3" t="str">
+        <v>Used Mango</v>
+      </c>
+      <c r="W3" t="str">
+        <v>Used Coco (Meat)</v>
+      </c>
+      <c r="X3" t="str">
+        <v>Used Coco (Water)</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Used Coco (Conden)</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>Used Coco (Raw)</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>Used Apple</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>Used Guava</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>Used Pineapple</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>Used Young Coco</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>Bottle Revenue (฿)</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>Source Note</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>01/10/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C4">
+        <v>2699</v>
+      </c>
+      <c r="D4">
+        <v>1890</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>809</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>9</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>40</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>Parn LINE photo 01M56Z0ZBJM60G0S61HHCMW2DT.jpg (B2 Daily Sales Record 01/10/26), hand-transcribed 2026-10-18 | sheet totals are after ice (cash 1830, grand 2639); booked before ice, ice in Expenses like B1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>02/10/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C5">
+        <v>3364</v>
+      </c>
+      <c r="D5">
+        <v>2090</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>1274</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>14</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>20</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>51</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>Parn LINE photo 01M56Z15SBMB2AJ72MF67WNAFF.jpg (B2 Daily Sales Record 02/10/26), hand-transcribed 2026-10-18 | sheet totals are after ice (cash 2030, grand 3304); booked before ice, ice in Expenses like B1 | CHECK: QR items 1,334 vs written 1,274 (+60)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>03/10/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C6">
+        <v>4304</v>
+      </c>
+      <c r="D6">
+        <v>2699</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="G6">
+        <v>1605</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>8</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>60</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>Parn LINE photo 01M56Z15M9VGJBP7BYXAYEMHN7.jpg (B2 Daily Sales Record 03/10/26), hand-transcribed 2026-10-18 | sheet totals are after ice (cash 2639, grand 4244); booked before ice, ice in Expenses like B1 | not in fruit columns: Grape 1, Pear 2, Pomegranate 5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>04/10/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C7">
+        <v>3608</v>
+      </c>
+      <c r="D7">
+        <v>2263</v>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+      <c r="G7">
+        <v>1345</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="J7">
+        <v>17</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>50</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>Parn LINE photo 01M56Z15FGPG5BS25GHH9YM5NC.jpg (B2 Daily Sales Record 04/10/26), hand-transcribed 2026-10-18 | sheet totals are after ice (cash 2203, grand 3548); booked before ice, ice in Expenses like B1 | not in fruit columns: Pomegranate 2, Grape 1, Grape (120) 1, Pear 3 | CHECK: cash items 2,253 vs written 2,263 (-10)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>05/10/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C8">
+        <v>2775</v>
+      </c>
+      <c r="D8">
+        <v>1890</v>
+      </c>
+      <c r="E8">
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <v>885</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>40</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>Parn LINE photo 01M56Z14Z0PDC1NC3BPYD52JAT.jpg (B2 Daily Sales Record 05/10/26), hand-transcribed 2026-10-18 | sheet totals are after ice (cash 1830, grand 2715); booked before ice, ice in Expenses like B1 | not in fruit columns: Pear 2, Grape 1, Pomegranate 1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>06/10/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C9">
+        <v>2234</v>
+      </c>
+      <c r="D9">
+        <v>1529</v>
+      </c>
+      <c r="E9">
+        <v>60</v>
+      </c>
+      <c r="G9">
+        <v>705</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>4</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>30</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>Parn LINE photo 01M56Z14T0V8CC9DFHRS56D9PQ.jpg (B2 Daily Sales Record 06/10/26), hand-transcribed 2026-10-18 | sheet totals are after ice (cash 1469, grand 2174); booked before ice, ice in Expenses like B1 | not in fruit columns: Pear 3, Pomegranate 3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>07/10/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C10">
+        <v>2605</v>
+      </c>
+      <c r="D10">
+        <v>1525</v>
+      </c>
+      <c r="E10">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>1080</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="J10">
+        <v>11</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>12</v>
+      </c>
+      <c r="M10">
+        <v>5</v>
+      </c>
+      <c r="O10">
+        <v>2</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>38</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>Parn LINE photo 01M56Z1446RJT12Q7FSDJR407H.jpg (B2 Daily Sales Record 07/10/26), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>08/10/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C11">
+        <v>2080</v>
+      </c>
+      <c r="D11">
+        <v>1115</v>
+      </c>
+      <c r="E11">
+        <v>60</v>
+      </c>
+      <c r="G11">
+        <v>965</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>6</v>
+      </c>
+      <c r="O11">
+        <v>6</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>33</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>Parn LINE photo 01M56Z14SM75C5WBM25A8RMMS8.jpg (B2 Daily Sales Record 08/10/26), hand-transcribed 2026-10-18 | sheet totals are after ice (cash 1055, grand 2020); booked before ice, ice in Expenses like B1 | not in fruit columns: Pear 3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>09/10/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C12">
+        <v>3200</v>
+      </c>
+      <c r="D12">
+        <v>2730</v>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>470</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>11</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>11</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>40</v>
+      </c>
+      <c r="AF12" t="str">
+        <v>Parn LINE photo 01M56Z141JFX6801S3WJCTH01P.jpg (B2 Daily Sales Record 09/10/26), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 8, Pear 2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>10/10/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C13">
+        <v>7064</v>
+      </c>
+      <c r="D13">
+        <v>4759</v>
+      </c>
+      <c r="E13">
+        <v>90</v>
+      </c>
+      <c r="G13">
+        <v>2305</v>
+      </c>
+      <c r="H13">
+        <v>9</v>
+      </c>
+      <c r="J13">
+        <v>33</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>18</v>
+      </c>
+      <c r="M13">
+        <v>4</v>
+      </c>
+      <c r="O13">
+        <v>5</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>96</v>
+      </c>
+      <c r="AF13" t="str">
+        <v>Parn LINE photo 01M56Z0ZC83MFZ6E6E3AN602KM.jpg (B2 Daily Sales Record 10/10/26), hand-transcribed 2026-10-18 | sheet totals are after ice (cash 4669, grand 6974); booked before ice, ice in Expenses like B1 | not in fruit columns: Pomegranate 10, Pear 7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>11/10/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C14">
+        <v>6005</v>
+      </c>
+      <c r="D14">
+        <v>4625</v>
+      </c>
+      <c r="E14">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>1380</v>
+      </c>
+      <c r="H14">
+        <v>8</v>
+      </c>
+      <c r="J14">
+        <v>26</v>
+      </c>
+      <c r="K14">
+        <v>9</v>
+      </c>
+      <c r="L14">
+        <v>7</v>
+      </c>
+      <c r="M14">
+        <v>15</v>
+      </c>
+      <c r="O14">
+        <v>7</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>81</v>
+      </c>
+      <c r="AF14" t="str">
+        <v>Parn LINE photo 01M56Z10B45G5BY8KB6VNWF1BG.jpg (B2 Daily Sales Record 11/10/26), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>12/10/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C15">
+        <v>6260</v>
+      </c>
+      <c r="D15">
+        <v>4050</v>
+      </c>
+      <c r="E15">
+        <v>120</v>
+      </c>
+      <c r="G15">
+        <v>2210</v>
+      </c>
+      <c r="H15">
+        <v>13</v>
+      </c>
+      <c r="J15">
+        <v>39</v>
+      </c>
+      <c r="K15">
+        <v>3</v>
+      </c>
+      <c r="L15">
+        <v>14</v>
+      </c>
+      <c r="M15">
+        <v>13</v>
+      </c>
+      <c r="O15">
+        <v>9</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>95</v>
+      </c>
+      <c r="AF15" t="str">
+        <v>Parn LINE photo 01M56Z12TMRXN4ANPV2TGN9Z5B.jpg (B2 Daily Sales Record 12/10/26), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>13/10/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C16">
+        <v>4019</v>
+      </c>
+      <c r="D16">
+        <v>1984</v>
+      </c>
+      <c r="E16">
+        <v>60</v>
+      </c>
+      <c r="G16">
+        <v>2035</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>10</v>
+      </c>
+      <c r="M16">
+        <v>14</v>
+      </c>
+      <c r="O16">
+        <v>4</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="str">
+        <v>Parn LINE photo 01M56Z0ZDFSRGCG6GRCTYJAE97.jpg (B2 Daily Sales Record 13/10/26), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C17">
+        <v>2485</v>
+      </c>
+      <c r="D17">
+        <v>1690</v>
+      </c>
+      <c r="E17">
+        <v>60</v>
+      </c>
+      <c r="G17">
+        <v>795</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>12</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <v>7</v>
+      </c>
+      <c r="M17">
+        <v>4</v>
+      </c>
+      <c r="O17">
+        <v>3</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>35</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>Parn LINE photo 01M56Z0ZB74KJXCFW22ZCM69CA.jpg (B2 Daily Sales Record 14/10/26), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>15/10/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C18">
+        <v>3630</v>
+      </c>
+      <c r="D18">
+        <v>1937</v>
+      </c>
+      <c r="E18">
+        <v>60</v>
+      </c>
+      <c r="G18">
+        <v>1693</v>
+      </c>
+      <c r="H18">
+        <v>8</v>
+      </c>
+      <c r="J18">
+        <v>14</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>5</v>
+      </c>
+      <c r="M18">
+        <v>5</v>
+      </c>
+      <c r="O18">
+        <v>8</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>46</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>Parn LINE photo 01M56Z10C2KT4J7NZNFGB0HRX1.jpg (B2 Daily Sales Record 15/10/26), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>16/10/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C19">
+        <v>4058</v>
+      </c>
+      <c r="D19">
+        <v>2743</v>
+      </c>
+      <c r="E19">
+        <v>60</v>
+      </c>
+      <c r="G19">
+        <v>1315</v>
+      </c>
+      <c r="H19">
+        <v>8</v>
+      </c>
+      <c r="J19">
+        <v>20</v>
+      </c>
+      <c r="K19">
+        <v>7</v>
+      </c>
+      <c r="L19">
+        <v>10</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="O19">
+        <v>6</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>56</v>
+      </c>
+      <c r="AF19" t="str">
+        <v>Parn LINE photo 01M56Z123JEEQQNSJGBRPBB9CP.jpg (B2 Daily Sales Record 16/10/26), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>17/10/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C20">
+        <v>3534</v>
+      </c>
+      <c r="D20">
+        <v>1639</v>
+      </c>
+      <c r="E20">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>1895</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>18</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>7</v>
+      </c>
+      <c r="M20">
+        <v>7</v>
+      </c>
+      <c r="O20">
+        <v>8</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>51</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>Parn LINE photo 01M56Z13TMVJBJY5H88SYRP0CP.jpg (B2 Daily Sales Record 17/10/26), hand-transcribed 2026-10-18 | not in fruit columns: Pomegranate 3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF20"/>
   </ignoredErrors>
 </worksheet>
 </file>
